--- a/artfynd/A 17748-2025 artfynd.xlsx
+++ b/artfynd/A 17748-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>111247791</v>
       </c>
       <c r="B2" t="n">
-        <v>84995</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>88962</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -726,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>659778.3494453959</v>
+        <v>659778</v>
       </c>
       <c r="R2" t="n">
-        <v>6704750.85900801</v>
+        <v>6704751</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,19 +754,9 @@
           <t>2023-08-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-08-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -809,66 +794,62 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111247508</v>
+        <v>111248561</v>
       </c>
       <c r="B3" t="n">
-        <v>96326</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>61491</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219798</v>
+        <v>106670</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svart skogssnigel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Arion ater ater</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lill-Kärven åt NNV, Upl</t>
+          <t>Lill-Kärven åt N, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>659698.3659643764</v>
+        <v>659764</v>
       </c>
       <c r="R3" t="n">
-        <v>6704757.705973366</v>
+        <v>6704754</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -898,19 +879,9 @@
           <t>2023-08-02</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-08-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,9 +894,14 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>skogsvägskant</t>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>granblodriska</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>granblodriska</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -940,6 +916,230 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>111247508</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lill-Kärven åt NNV, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>659698</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6704758</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-08-02</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-08-02</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>skogsvägskant</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Kerstin Frostberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Kerstin Frostberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>127505106</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99153</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kärven, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>659853</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6704509</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17748-2025 artfynd.xlsx
+++ b/artfynd/A 17748-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111247791</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -916,6 +926,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111248561</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1035,6 +1050,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111247508</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1140,8 +1160,19 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127505106</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>